--- a/Pet_Info.xlsx
+++ b/Pet_Info.xlsx
@@ -7,9 +7,8 @@
     <workbookView windowWidth="30720" windowHeight="12935"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="宠物信息" sheetId="2" r:id="rId1"/>
+    <sheet name="版本信息" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1727" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1738" uniqueCount="808">
   <si>
     <t>编号</t>
   </si>
@@ -2420,6 +2419,39 @@
   </si>
   <si>
     <t>暮星辰</t>
+  </si>
+  <si>
+    <t>字段</t>
+  </si>
+  <si>
+    <t>值</t>
+  </si>
+  <si>
+    <t>版本号</t>
+  </si>
+  <si>
+    <t>1.0.1</t>
+  </si>
+  <si>
+    <t>更新日期</t>
+  </si>
+  <si>
+    <t>更新内容</t>
+  </si>
+  <si>
+    <t>新增版本信息</t>
+  </si>
+  <si>
+    <t>更新者</t>
+  </si>
+  <si>
+    <t>这货不是莫谙</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>洛克王国：世界宠物评分数据</t>
   </si>
 </sst>
 </file>
@@ -3035,9 +3067,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3353,11 +3392,11 @@
   <dimension ref="A1:F348"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="5.66666666666667" customWidth="1"/>
-    <col min="2" max="2" width="11.8888888888889" customWidth="1"/>
-    <col min="3" max="3" width="5.66666666666667" customWidth="1"/>
-    <col min="4" max="4" width="42.2222222222222" customWidth="1"/>
-    <col min="5" max="6" width="16.4444444444444" customWidth="1"/>
+    <col min="1" max="1" width="5.66666666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.8888888888889" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.66666666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="42.2222222222222" style="1" customWidth="1"/>
+    <col min="5" max="6" width="16.4444444444444" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -10288,23 +10327,63 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="15" style="1" customWidth="1"/>
+    <col min="2" max="2" width="40" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>797</v>
+      </c>
+      <c r="B1" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>799</v>
+      </c>
+      <c r="B2" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>801</v>
+      </c>
+      <c r="B3" s="2">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>802</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>804</v>
+      </c>
+      <c r="B5" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>806</v>
+      </c>
+      <c r="B6" t="s">
+        <v>807</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/Pet_Info.xlsx
+++ b/Pet_Info.xlsx
@@ -2430,7 +2430,7 @@
     <t>版本号</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.0.2</t>
   </si>
   <si>
     <t>更新日期</t>

--- a/Pet_Info.xlsx
+++ b/Pet_Info.xlsx
@@ -2430,7 +2430,7 @@
     <t>版本号</t>
   </si>
   <si>
-    <t>1.0.2</t>
+    <t>1.0.3</t>
   </si>
   <si>
     <t>更新日期</t>
